--- a/project/analysis/financial_analysis.xlsx
+++ b/project/analysis/financial_analysis.xlsx
@@ -8,12 +8,11 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="شاخص‌های کلیدی" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="تحلیل قرارداد" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="آمار روزانه" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="سهمیه مصرف" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="اقدامات کنترل هزینه" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="تعمیرات و تجهیزات" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="موارد عدم انطباق" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="آمار روزانه" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="سهمیه مصرف" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="اقدامات کنترل هزینه" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="تعمیرات و تجهیزات" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="موارد عدم انطباق" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -482,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -561,305 +560,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>قرارداد خدماتی تحت نظارت</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C17"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>شرح</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>مقدار</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>واحد</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>مبلغ هر سرویس (ریال)</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="n">
-        <v>22000000</v>
-      </c>
-      <c r="C2" s="6" t="inlineStr">
-        <is>
-          <t>ریال</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>تعداد سرویس در سال</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="n">
-        <v>300</v>
-      </c>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>سرویس</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>سقف مبلغ قرارداد (ریال)</t>
-        </is>
-      </c>
-      <c r="B4" s="5">
-        <f>B2*B3</f>
-        <v/>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>ریال</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>نرخ کسر بیمه ماده ۳۸</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>درصد</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>مبلغ کسر بیمه از سقف قرارداد</t>
-        </is>
-      </c>
-      <c r="B6" s="5">
-        <f>B4*B5</f>
-        <v/>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>ریال</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>نرخ سپرده حسن انجام کار</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>درصد</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>مبلغ سپرده حسن انجام کار</t>
-        </is>
-      </c>
-      <c r="B8" s="5">
-        <f>B4*B7</f>
-        <v/>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>ریال</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>نرخ تضمین (چک صیادی)</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>درصد</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>مبلغ تضمین</t>
-        </is>
-      </c>
-      <c r="B10" s="5">
-        <f>B4*B9</f>
-        <v/>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>ریال</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>نرخ جریمه تأخیر روزانه</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>درصد</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>سقف جریمه تأخیر</t>
-        </is>
-      </c>
-      <c r="B12" s="5">
-        <f>B4*0.10</f>
-        <v/>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>ریال</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>نرخ هزینه بالاسری</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>درصد</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>سقف تغییر مقادیر قرارداد</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>درصد</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>مبلغ قابل تغییر (ریال)</t>
-        </is>
-      </c>
-      <c r="B15" s="5">
-        <f>B4*B14</f>
-        <v/>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>ریال</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>مدت قرارداد (ماه)</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>ماه</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>میانگین سرویس ماهانه</t>
-        </is>
-      </c>
-      <c r="B17" s="5">
-        <f>B3/B16</f>
-        <v/>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>سرویس</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1754,7 +1460,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1909,13 +1615,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -2059,29 +1765,12 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>الزام پیمانکاران به تهیه غذا صرفاً از رستوران شرکت مادکوش</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>تثبیت تقاضای خدمات رستوران</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>قراردادی</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2299,7 +1988,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
